--- a/new try - stepupp/marks_data.xlsx
+++ b/new try - stepupp/marks_data.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F375"/>
+  <dimension ref="A1:F499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>100</v>
@@ -544,10 +544,8 @@
       <c r="D3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
+      <c r="E3" s="4" t="n">
+        <v>92</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>100</v>
@@ -2137,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>100</v>
@@ -3751,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F126" s="4" t="n">
         <v>100</v>
@@ -5365,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F188" s="4" t="n">
         <v>100</v>
@@ -6981,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F250" s="4" t="n">
         <v>100</v>
@@ -8605,7 +8603,7 @@
         <v>1</v>
       </c>
       <c r="E312" s="4" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F312" s="4" t="n">
         <v>100</v>
@@ -10259,6 +10257,3246 @@
       </c>
       <c r="F375" s="4" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="376" ht="20" customHeight="1">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>911524205001</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>ABICHETHRA P</t>
+        </is>
+      </c>
+      <c r="C376" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E376" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F376" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="377" ht="20" customHeight="1">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>911524205002</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>ABIRAMI K</t>
+        </is>
+      </c>
+      <c r="C377" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E377" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F377" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="378" ht="20" customHeight="1">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>911524205003</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>AFRIN JAISHA S</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E378" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F378" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="379" ht="20" customHeight="1">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>911524205004</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>AHAMED RASIK FARITH S</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E379" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F379" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="380" ht="20" customHeight="1">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>911524205005</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>AHAMED SHAKI Z</t>
+        </is>
+      </c>
+      <c r="C380" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E380" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F380" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="381" ht="20" customHeight="1">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>911524205006</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>AL AFRAAH S</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E381" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F381" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="382" ht="20" customHeight="1">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>911524205007</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>ALBUNVINOJ D</t>
+        </is>
+      </c>
+      <c r="C382" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E382" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F382" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="383" ht="20" customHeight="1">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>911524205008</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>APRITH LENAN R J</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E383" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F383" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="384" ht="20" customHeight="1">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>911524205009</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>ASLAN SHA A</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E384" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F384" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="385" ht="20" customHeight="1">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>911524205010</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>BAHIYA SRI K</t>
+        </is>
+      </c>
+      <c r="C385" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E385" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F385" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="386" ht="20" customHeight="1">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>911524205011</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>BALAGANESH V</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E386" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F386" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="387" ht="20" customHeight="1">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>911524205012</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>DEVIKA P</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E387" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F387" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="388" ht="20" customHeight="1">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>911524205013</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>EDINA SHERIN A</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E388" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F388" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="389" ht="20" customHeight="1">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>911524205015</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>FAHIMA PARVEEN W</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E389" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F389" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="390" ht="20" customHeight="1">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>911524205016</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>FATHIMA FARHA M</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E390" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F390" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="391" ht="20" customHeight="1">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>911524205017</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>HARISH KUMAR R</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E391" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F391" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="392" ht="20" customHeight="1">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>911524205018</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>HARSHINI R</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E392" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F392" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="393" ht="20" customHeight="1">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>911524205019</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>ISMAIL D</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E393" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F393" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="394" ht="20" customHeight="1">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>911524205020</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>JEEVA N</t>
+        </is>
+      </c>
+      <c r="C394" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E394" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F394" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="395" ht="20" customHeight="1">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>911524205021</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>KALINIRANJAN K</t>
+        </is>
+      </c>
+      <c r="C395" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E395" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F395" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="396" ht="20" customHeight="1">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>911524205022</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>KARAN M</t>
+        </is>
+      </c>
+      <c r="C396" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E396" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F396" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="397" ht="20" customHeight="1">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>911524205023</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>KEERTHIGA M</t>
+        </is>
+      </c>
+      <c r="C397" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E397" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F397" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="398" ht="20" customHeight="1">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>911524205024</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>LAKSHMI NARAYANAN</t>
+        </is>
+      </c>
+      <c r="C398" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E398" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F398" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="399" ht="20" customHeight="1">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>911524205025</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>LITHISH K</t>
+        </is>
+      </c>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E399" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F399" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="400" ht="20" customHeight="1">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>911524205026</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>MATHANBABU M</t>
+        </is>
+      </c>
+      <c r="C400" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E400" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F400" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="401" ht="20" customHeight="1">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>911524205027</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED AATHIF H</t>
+        </is>
+      </c>
+      <c r="C401" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E401" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F401" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="402" ht="20" customHeight="1">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>911524205028</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED FAREETH K</t>
+        </is>
+      </c>
+      <c r="C402" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E402" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F402" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="403" ht="20" customHeight="1">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>911524205029</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED HAJA NAWAS J</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E403" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F403" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="404" ht="20" customHeight="1">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>911524205030</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED NIHMATHULLAH S</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E404" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F404" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="405" ht="20" customHeight="1">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>911524205031</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED SAJEER S</t>
+        </is>
+      </c>
+      <c r="C405" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E405" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F405" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="406" ht="20" customHeight="1">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>911524205032</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED SHEEDHU N</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E406" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F406" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="407" ht="20" customHeight="1">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>911524205033</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED THAMEEM ANSARI S</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E407" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F407" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="408" ht="20" customHeight="1">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>911524205034</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>MUNEESWARAN S</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E408" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F408" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="409" ht="20" customHeight="1">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>911524205035</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>NAAZIR MEERAN K</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E409" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F409" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="410" ht="20" customHeight="1">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>911524205036</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>NANDHINI R</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E410" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F410" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="411" ht="20" customHeight="1">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>911524205037</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr">
+        <is>
+          <t>NIKILAN A</t>
+        </is>
+      </c>
+      <c r="C411" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E411" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F411" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="412" ht="20" customHeight="1">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>911524205038</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>NOORUL THAHANI K</t>
+        </is>
+      </c>
+      <c r="C412" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E412" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F412" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="413" ht="20" customHeight="1">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>911524205039</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr">
+        <is>
+          <t>PAZHANI LAVANYA S</t>
+        </is>
+      </c>
+      <c r="C413" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E413" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F413" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="414" ht="20" customHeight="1">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>911524205040</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>PRITHIVIRAJ S</t>
+        </is>
+      </c>
+      <c r="C414" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E414" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F414" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="415" ht="20" customHeight="1">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>911524205041</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="inlineStr">
+        <is>
+          <t>RAHUL SANJAY R</t>
+        </is>
+      </c>
+      <c r="C415" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="416" ht="20" customHeight="1">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>911524205042</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>ROHITH RAJA A</t>
+        </is>
+      </c>
+      <c r="C416" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F416" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="417" ht="20" customHeight="1">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>911524205043</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="inlineStr">
+        <is>
+          <t>SAFRAN AATHIKA H</t>
+        </is>
+      </c>
+      <c r="C417" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E417" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F417" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="418" ht="20" customHeight="1">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>911524205044</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>SANJEEVPRAKASH S</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E418" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F418" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="419" ht="20" customHeight="1">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>911524205045</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>SARAFATH AHMED S</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E419" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F419" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="420" ht="20" customHeight="1">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>911524205046</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>SHABIYA THABASUM M</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E420" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F420" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="421" ht="20" customHeight="1">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>911524205047</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>SHAFAANA KHAALIDA S</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E421" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F421" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="422" ht="20" customHeight="1">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>911524205048</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>SHAKILA SRI T</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E422" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F422" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="423" ht="20" customHeight="1">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>911524205050</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>SIBI SHARVESH M</t>
+        </is>
+      </c>
+      <c r="C423" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E423" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F423" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="424" ht="20" customHeight="1">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>911524205051</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>SIFAUL ZABEEN M</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E424" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F424" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="425" ht="20" customHeight="1">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>911524205052</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>SUMAIYA S</t>
+        </is>
+      </c>
+      <c r="C425" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E425" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F425" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="426" ht="20" customHeight="1">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>911524205053</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>SWARNIKA B</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E426" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F426" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="427" ht="20" customHeight="1">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>911524205301</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>ABRISH SANJAI R</t>
+        </is>
+      </c>
+      <c r="C427" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E427" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F427" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="428" ht="20" customHeight="1">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>911524205302</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>DEVNATH C</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E428" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F428" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="429" ht="20" customHeight="1">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>911524205303</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>KANAGAVEL J</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E429" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F429" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="430" ht="20" customHeight="1">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>911524205304</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR S</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E430" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F430" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="431" ht="20" customHeight="1">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>911524205305</t>
+        </is>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED ASLAM S M</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E431" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F431" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="432" ht="20" customHeight="1">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>911524205306</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED HAAFIL H</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E432" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F432" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="433" ht="20" customHeight="1">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>911524205307</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED JASIR H</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E433" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F433" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="434" ht="20" customHeight="1">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>911524205308</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>RUTHISKAVI K</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F434" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="435" ht="20" customHeight="1">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>911524205309</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>SAMIH ANSAR A</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F435" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="436" ht="20" customHeight="1">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>911524205310</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>SYED ASHAKKEEN A</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E436" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F436" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="437" ht="20" customHeight="1">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>911524205311</t>
+        </is>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>VISHWA S</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="inlineStr">
+        <is>
+          <t>Cloud computing</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E437" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F437" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="438" ht="20" customHeight="1">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>911524205001</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>ABICHETHRA P</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E438" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F438" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="439" ht="20" customHeight="1">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>911524205002</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>ABIRAMI K</t>
+        </is>
+      </c>
+      <c r="C439" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E439" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F439" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="440" ht="20" customHeight="1">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>911524205003</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>AFRIN JAISHA S</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E440" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F440" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="441" ht="20" customHeight="1">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>911524205004</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>AHAMED RASIK FARITH S</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E441" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F441" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="442" ht="20" customHeight="1">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>911524205005</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="inlineStr">
+        <is>
+          <t>AHAMED SHAKI Z</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E442" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F442" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="443" ht="20" customHeight="1">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>911524205006</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>AL AFRAAH S</t>
+        </is>
+      </c>
+      <c r="C443" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E443" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F443" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="444" ht="20" customHeight="1">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>911524205007</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="inlineStr">
+        <is>
+          <t>ALBUNVINOJ D</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E444" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F444" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="445" ht="20" customHeight="1">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>911524205008</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>APRITH LENAN R J</t>
+        </is>
+      </c>
+      <c r="C445" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E445" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F445" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="446" ht="20" customHeight="1">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>911524205009</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="inlineStr">
+        <is>
+          <t>ASLAN SHA A</t>
+        </is>
+      </c>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E446" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F446" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="447" ht="20" customHeight="1">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>911524205010</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>BAHIYA SRI K</t>
+        </is>
+      </c>
+      <c r="C447" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E447" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F447" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="448" ht="20" customHeight="1">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>911524205011</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="inlineStr">
+        <is>
+          <t>BALAGANESH V</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E448" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F448" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="449" ht="20" customHeight="1">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>911524205012</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>DEVIKA P</t>
+        </is>
+      </c>
+      <c r="C449" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E449" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F449" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="450" ht="20" customHeight="1">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>911524205013</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="inlineStr">
+        <is>
+          <t>EDINA SHERIN A</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E450" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F450" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="451" ht="20" customHeight="1">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>911524205015</t>
+        </is>
+      </c>
+      <c r="B451" s="3" t="inlineStr">
+        <is>
+          <t>FAHIMA PARVEEN W</t>
+        </is>
+      </c>
+      <c r="C451" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E451" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F451" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="452" ht="20" customHeight="1">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>911524205016</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="inlineStr">
+        <is>
+          <t>FATHIMA FARHA M</t>
+        </is>
+      </c>
+      <c r="C452" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E452" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F452" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="453" ht="20" customHeight="1">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>911524205017</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="inlineStr">
+        <is>
+          <t>HARISH KUMAR R</t>
+        </is>
+      </c>
+      <c r="C453" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E453" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F453" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="454" ht="20" customHeight="1">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>911524205018</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>HARSHINI R</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E454" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F454" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="455" ht="20" customHeight="1">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>911524205019</t>
+        </is>
+      </c>
+      <c r="B455" s="3" t="inlineStr">
+        <is>
+          <t>ISMAIL D</t>
+        </is>
+      </c>
+      <c r="C455" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E455" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F455" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="456" ht="20" customHeight="1">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>911524205020</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>JEEVA N</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E456" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F456" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="457" ht="20" customHeight="1">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>911524205021</t>
+        </is>
+      </c>
+      <c r="B457" s="3" t="inlineStr">
+        <is>
+          <t>KALINIRANJAN K</t>
+        </is>
+      </c>
+      <c r="C457" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E457" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F457" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="458" ht="20" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>911524205022</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>KARAN M</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E458" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="F458" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="459" ht="20" customHeight="1">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>911524205023</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="inlineStr">
+        <is>
+          <t>KEERTHIGA M</t>
+        </is>
+      </c>
+      <c r="C459" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E459" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F459" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="460" ht="20" customHeight="1">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>911524205024</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>LAKSHMI NARAYANAN</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E460" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F460" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="461" ht="20" customHeight="1">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>911524205025</t>
+        </is>
+      </c>
+      <c r="B461" s="3" t="inlineStr">
+        <is>
+          <t>LITHISH K</t>
+        </is>
+      </c>
+      <c r="C461" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E461" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F461" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="462" ht="20" customHeight="1">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>911524205026</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>MATHANBABU M</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E462" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F462" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="463" ht="20" customHeight="1">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>911524205027</t>
+        </is>
+      </c>
+      <c r="B463" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED AATHIF H</t>
+        </is>
+      </c>
+      <c r="C463" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E463" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F463" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="464" ht="20" customHeight="1">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>911524205028</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED FAREETH K</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E464" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F464" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="465" ht="20" customHeight="1">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>911524205029</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED HAJA NAWAS J</t>
+        </is>
+      </c>
+      <c r="C465" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E465" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F465" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="466" ht="20" customHeight="1">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>911524205030</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED NIHMATHULLAH S</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E466" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F466" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="467" ht="20" customHeight="1">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>911524205031</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED SAJEER S</t>
+        </is>
+      </c>
+      <c r="C467" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E467" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F467" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="468" ht="20" customHeight="1">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>911524205032</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED SHEEDHU N</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E468" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F468" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="469" ht="20" customHeight="1">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>911524205033</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED THAMEEM ANSARI S</t>
+        </is>
+      </c>
+      <c r="C469" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E469" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F469" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="470" ht="20" customHeight="1">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>911524205034</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>MUNEESWARAN S</t>
+        </is>
+      </c>
+      <c r="C470" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E470" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F470" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="471" ht="20" customHeight="1">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>911524205035</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>NAAZIR MEERAN K</t>
+        </is>
+      </c>
+      <c r="C471" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E471" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F471" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="472" ht="20" customHeight="1">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>911524205036</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>NANDHINI R</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E472" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F472" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="473" ht="20" customHeight="1">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>911524205037</t>
+        </is>
+      </c>
+      <c r="B473" s="3" t="inlineStr">
+        <is>
+          <t>NIKILAN A</t>
+        </is>
+      </c>
+      <c r="C473" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E473" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F473" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="474" ht="20" customHeight="1">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>911524205038</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>NOORUL THAHANI K</t>
+        </is>
+      </c>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E474" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F474" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="475" ht="20" customHeight="1">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>911524205039</t>
+        </is>
+      </c>
+      <c r="B475" s="3" t="inlineStr">
+        <is>
+          <t>PAZHANI LAVANYA S</t>
+        </is>
+      </c>
+      <c r="C475" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E475" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F475" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="476" ht="20" customHeight="1">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>911524205040</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>PRITHIVIRAJ S</t>
+        </is>
+      </c>
+      <c r="C476" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E476" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F476" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="477" ht="20" customHeight="1">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>911524205041</t>
+        </is>
+      </c>
+      <c r="B477" s="3" t="inlineStr">
+        <is>
+          <t>RAHUL SANJAY R</t>
+        </is>
+      </c>
+      <c r="C477" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E477" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F477" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="478" ht="20" customHeight="1">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>911524205042</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>ROHITH RAJA A</t>
+        </is>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E478" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F478" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="479" ht="20" customHeight="1">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>911524205043</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="inlineStr">
+        <is>
+          <t>SAFRAN AATHIKA H</t>
+        </is>
+      </c>
+      <c r="C479" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E479" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F479" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="480" ht="20" customHeight="1">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>911524205044</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>SANJEEVPRAKASH S</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E480" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F480" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="481" ht="20" customHeight="1">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>911524205045</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="inlineStr">
+        <is>
+          <t>SARAFATH AHMED S</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E481" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F481" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="482" ht="20" customHeight="1">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>911524205046</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>SHABIYA THABASUM M</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E482" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F482" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="483" ht="20" customHeight="1">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>911524205047</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="inlineStr">
+        <is>
+          <t>SHAFAANA KHAALIDA S</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D483" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E483" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="F483" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="484" ht="20" customHeight="1">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>911524205048</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>SHAKILA SRI T</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E484" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F484" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="485" ht="20" customHeight="1">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>911524205050</t>
+        </is>
+      </c>
+      <c r="B485" s="3" t="inlineStr">
+        <is>
+          <t>SIBI SHARVESH M</t>
+        </is>
+      </c>
+      <c r="C485" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D485" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E485" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F485" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="486" ht="20" customHeight="1">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>911524205051</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>SIFAUL ZABEEN M</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E486" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F486" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="487" ht="20" customHeight="1">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>911524205052</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>SUMAIYA S</t>
+        </is>
+      </c>
+      <c r="C487" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E487" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F487" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="488" ht="20" customHeight="1">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>911524205053</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>SWARNIKA B</t>
+        </is>
+      </c>
+      <c r="C488" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E488" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="F488" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="489" ht="20" customHeight="1">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>911524205301</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>ABRISH SANJAI R</t>
+        </is>
+      </c>
+      <c r="C489" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D489" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E489" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F489" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="490" ht="20" customHeight="1">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>911524205302</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>DEVNATH C</t>
+        </is>
+      </c>
+      <c r="C490" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E490" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F490" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="491" ht="20" customHeight="1">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>911524205303</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>KANAGAVEL J</t>
+        </is>
+      </c>
+      <c r="C491" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F491" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="492" ht="20" customHeight="1">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>911524205304</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR S</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E492" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="F492" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="493" ht="20" customHeight="1">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>911524205305</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED ASLAM S M</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E493" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F493" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="494" ht="20" customHeight="1">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>911524205306</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED HAAFIL H</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E494" s="4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F494" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="495" ht="20" customHeight="1">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>911524205307</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMED JASIR H</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E495" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F495" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="496" ht="20" customHeight="1">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>911524205308</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>RUTHISKAVI K</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E496" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F496" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="497" ht="20" customHeight="1">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>911524205309</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="inlineStr">
+        <is>
+          <t>SAMIH ANSAR A</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D497" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E497" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F497" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="498" ht="20" customHeight="1">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>911524205310</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>SYED ASHAKKEEN A</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E498" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="F498" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="499" ht="20" customHeight="1">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>911524205311</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="inlineStr">
+        <is>
+          <t>VISHWA S</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>UI&amp;UX designing</t>
+        </is>
+      </c>
+      <c r="D499" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E499" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F499" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
